--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0173.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0173.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Toàn những lời này khiến ta lại thèm một chuyến trốn chạy khỏi cuộc sống ở đây. Vậy... lần này chúng ta nên đi đâu nhỉ?</t>
+          <t>Toàn những lời này khiến tao lại thèm một chuyến trốn chạy khỏi cuộc sống ở đây. Vậy... lần này chúng ta nên đi đâu nhỉ?</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sao cậu biết?</t>
+          <t>Sao cậu biết được?</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Quý bà Carolina, cuộc thương thuyết tại Lâu đài Porto-Veno diễn ra thế nào rồi?</t>
+          <t>Quý bà Carolina, cuộc thương thuyết tại Porto-Veno Castle diễn ra thế nào rồi?</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Đến Lâu đài Porto-Veno và trả lại chiếc trâm này cho gia tộc Montelli</t>
+          <t>Đến Porto-Veno Castle và trả lại chiếc trâm này cho gia tộc Montelli</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Nhớ mang về cho ta vài câu chuyện thú vị nhé!</t>
+          <t>Nhớ mang về cho tao vài câu chuyện thú vị nhé!</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Chết tiệt! Là kính viễn vọng! Tuyệt quá! Giờ ta có thể thấy Ragunna nhộn nhịp rồi!</t>
+          <t>Chết tiệt! Là kính viễn vọng! Tuyệt quá! Giờ tao có thể thấy Ragunna nhộn nhịp rồi!</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ta tưởng mọi người đã quên bài hát này rồi. Nghe lại mới thấy nhớ thời niên thiếu...</t>
+          <t>Tao tưởng mọi người đã quên bài hát này rồi. Nghe lại mới thấy nhớ thời niên thiếu...</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Aaa—bộ đồ mới của ta vừa bị thủng một lỗ cháy đấy!</t>
+          <t>Aaa—bộ đồ mới của tao vừa bị thủng một lỗ cháy đấy!</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cái bầu nước cậu đang đeo là Thiết bị đầu cuối Dự phòng phải không? Ồ, đừng lo. Ta không đến để kiểm tra Thiết bị đầu cuối của cậu đâu.</t>
+          <t>Cái bầu nước cậu đang đeo là Thiết bị đầu cuối Dự phòng phải không? Ồ, đừng lo. Tao không đến để kiểm tra Thiết bị đầu cuối của cậu đâu.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Tulio... *thở dài*... Phải thừa nhận, trong Hội Phục Tùng, hắn là người am hiểu nhất về Tiếng Vang.</t>
+          <t>Tulio... *thở dài*... Phải thừa nhận, trong Hội Phục Tùng, hắn là người am hiểu nhất về Echo.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Một số thuật ngữ kinh doanh của cậu làm ta rối cả đầu.</t>
+          <t>Một số thuật ngữ kinh doanh của cậu làm tao rối cả đầu.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Chưa đến bao giờ à? Những trận đấu ở đấu trường đó mới tuyệt làm sao, toàn là những Cộng Hưởng Giả Echo thi đấu ấy! Chắc chắn ta sẽ lẻn đi xem vài trận khi đến nơi.</t>
+          <t>Chưa đến bao giờ à? Những trận đấu ở đấu trường đó mới tuyệt làm sao, toàn là những Cộng Hưởng Giả Echo thi đấu ấy! Chắc chắn tao sẽ lẻn đi xem vài trận khi đến nơi.</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Thề có Hoàng Đế! Có lẽ ta nên tống ngươi vào Nhà Tù Sám Hối ngay lập tức. Ngươi nên ở trên Thuyền Hành Hương mà ăn năn tội lỗi đi!</t>
+          <t>Thề có Hoàng Đế! Có lẽ tao nên tống mày vào Nhà Tù Sám Hối ngay lập tức. Mày nên ở trên Thuyền Hành Hương mà ăn năn tội lỗi đi!</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Ta tin Hiệp hội Tiên phong có thể hỗ trợ dự án này. Nếu cậu quan tâm, sao không ghé qua studio của tụi ta để thảo luận chi tiết khi cậu rảnh?</t>
+          <t>Tao tin Hiệp hội Tiên phong có thể hỗ trợ dự án này. Nếu cậu quan tâm, sao không ghé qua studio của tụi tao để thảo luận chi tiết khi cậu rảnh?</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Những kẻ tiên phong của New Federation dạo này chẳng tung ra được cái gì thú vị. Ta có linh cảm là tiền của chúng ta coi như đi tong rồi.</t>
+          <t>Những kẻ tiên phong của New Federation dạo này chẳng tung ra được cái gì thú vị. Tao có linh cảm là tiền của chúng ta coi như đi tong rồi.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Một số thuật ngữ kinh doanh của cậu làm ta rối cả đầu.</t>
+          <t>Một số thuật ngữ kinh doanh của cậu làm tao rối cả đầu.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Hay để ta chết ngoài biển khơi, không bao giờ trở về nhà!</t>
+          <t>Hay để tao chết ngoài biển khơi, không bao giờ trở về nhà!</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cậu đếm cái gì vậy?</t>
+          <t>Mày đếm cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Thằng cha Barbosa đó bắt ta đếm từng đồng Monnaie cũ kỹ gửi vào kho.</t>
+          <t>Thằng cha Barbosa đó bắt tao đếm từng đồng Monnaie cũ kỹ gửi vào kho.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Sếp càng bất tài, cái tôi của hắn càng mong manh. Ta đã cảnh cáo ngươi đừng chống lại hắn rồi. Giờ hắn sẽ làm gương ngươi thôi.</t>
+          <t>Sếp càng bất tài, cái tôi của hắn càng mong manh. Tao đã cảnh cáo mày đừng chống lại hắn rồi. Giờ hắn sẽ làm gương mày thôi.</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Chết tiệt! Sợ hết vía! Ta tưởng lại gặp phải sếp rồi.</t>
+          <t>Chết tiệt! Sợ hết vía! Tao tưởng lại gặp phải sếp rồi.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Thì đã sao nếu ta phải dùng chiêu bẩn, chơi xấu!</t>
+          <t>Thì đã sao nếu tao phải dùng chiêu bẩn, chơi xấu!</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đã sắp xếp xong rồi, Davi à – ý ta là, vị khách hàng ẩn danh.</t>
+          <t>Đã sắp xếp xong rồi, Davi à – ý tao là, vị khách hàng ẩn danh.</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ha, thảo nào Giovanni không dám đi gặp bà ta một mình và kéo ta theo...</t>
+          <t>Ha, thảo nào Giovanni không dám đi gặp bà ta một mình và kéo tao theo...</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ta sẽ không bàn về chủ đề đó vì ngươi nên biết rồi. Lần này, ta sẽ chỉ nói về phong tục ăn uống thôi.</t>
+          <t>Tao sẽ không bàn về chủ đề đó vì mày nên biết rồi. Lần này, tao sẽ chỉ nói về phong tục ăn uống thôi.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Ôi trời, kinh quá! Được rồi, ta hiểu ý cậu rồi.</t>
+          <t>Ôi trời, kinh quá! Được rồi, tao hiểu ý cậu rồi.</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Hả? Ai đang nghe lén đấy? Ngươi định ăn cắp kỹ thuật &lt;ano=Echo tuning&gt;điều chỉnh&lt;/ano&gt; Echo của ta à?</t>
+          <t>Hả? Ai đang nghe lén đấy? Mày định ăn cắp kỹ thuật &lt;ano=Echo tuning&gt;điều chỉnh&lt;/ano&gt; Echo của tao à?</t>
         </is>
       </c>
     </row>
